--- a/data/ct_scoop/ct_scoop_links_2026-05-14.xlsx
+++ b/data/ct_scoop/ct_scoop_links_2026-05-14.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,127 +440,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MANCHESTER SCOOP: Moran Restaurant reopens under new owners</t>
+          <t>STORRS SCOOP: Chipotle Mexican Grill planned for Storrs Center</t>
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-moran-restaurant-reopens-under-new-owners</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/storrs-scoop-chipotle-mexican-grill-planned-for-storrs-center</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NORTH HAVEN SCOOP: 7 Brew sets opening date!</t>
+          <t>HARTFORD SCOOP: New Ice Cream &amp; Coffee Shop coming to State House Square</t>
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/north-haven-scoop-7-brew-sets-opening-date</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/hartford-scoop-new-ice-cream-coffee-shop-coming-to-state-house-square</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORANGE SCOOP: The Wok Chinese Kitchen coming to former Five Guys space</t>
+          <t>BRANFORD SCOOP: Home Restaurant closing in Branford after 14 years</t>
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/orange-scoop-the-wok-chinese-kitchen-coming-to-former-five-guys-space</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/branford-scoop-home-restaurant-closing-in-branford-after-14-years</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LEDYARD SCOOP: Two Trees Inn reopens near Foxwoods</t>
+          <t>WEST SPRINGFIELD SCOOP: Yemerica bringing Yemeni coffee to West Springfield!</t>
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/ledyard-scoop-two-trees-inn-reopens-near-foxwoods</t>
+          <t>https://www.theconnecticutscoop.com/all-mass-posts/west-springfield-scoop-yemerica-bringing-yemeni-coffee-to-west-springfield</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ELLINGTON SCOOP: Review of Wen Ming House's new AYCE menu</t>
+          <t>MANCHESTER SCOOP: Moran Restaurant reopens under new owners</t>
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/ellington-scoop-review-of-wen-ming-houses-new-ayce-menu</t>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/manchester-scoop-moran-restaurant-reopens-under-new-owners</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOUTH WINDSOR SCOOP: New pottery studio opening later this month!</t>
+          <t>NORTH HAVEN SCOOP: 7 Brew sets opening date!</t>
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-new-pottery-studio-opening-later-this-month</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/north-haven-scoop-7-brew-sets-opening-date</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEWINGTON SCOOP: Large-scale development eyed in Newington</t>
+          <t>ORANGE SCOOP: The Wok Chinese Kitchen coming to former Five Guys space</t>
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-large-scale-development-eyed-in-newington</t>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/orange-scoop-the-wok-chinese-kitchen-coming-to-former-five-guys-space</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MERIDEN SCOOP: Furnish Cheap by Universal Hotel Liquidators opens at Meriden Mall</t>
+          <t>LEDYARD SCOOP: Two Trees Inn reopens near Foxwoods</t>
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-furnish-cheap-by-universal-hotel-liquidators-opens-at-meriden-mall</t>
+          <t>https://www.theconnecticutscoop.com/all-new-london-county-posts/ledyard-scoop-two-trees-inn-reopens-near-foxwoods</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DANBURY SCOOP: Paris Baguette coming soon to Danbury Fair</t>
+          <t>ELLINGTON SCOOP: Review of Wen Ming House's new AYCE menu</t>
         </is>
       </c>
       <c r="B10" s="1" t="n">
@@ -568,20 +568,80 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/danbury-scoop-paris-baguette-coming-soon-to-danbury-fair</t>
+          <t>https://www.theconnecticutscoop.com/all-tolland-county-posts/ellington-scoop-review-of-wen-ming-houses-new-ayce-menu</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CROMWELL SCOOP: Wingstop coming to Cromwell</t>
+          <t>SOUTH WINDSOR SCOOP: New pottery studio opening later this month!</t>
         </is>
       </c>
       <c r="B11" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/south-windsor-scoop-new-pottery-studio-opening-later-this-month</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEWINGTON SCOOP: Large-scale development eyed in Newington</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-hartford-county-posts/newington-scoop-large-scale-development-eyed-in-newington</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MERIDEN SCOOP: Furnish Cheap by Universal Hotel Liquidators opens at Meriden Mall</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-new-haven-county-posts/meriden-scoop-furnish-cheap-by-universal-hotel-liquidators-opens-at-meriden-mall</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DANBURY SCOOP: Paris Baguette coming soon to Danbury Fair</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.theconnecticutscoop.com/all-fairfield-county-posts/danbury-scoop-paris-baguette-coming-soon-to-danbury-fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CROMWELL SCOOP: Wingstop coming to Cromwell</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://www.theconnecticutscoop.com/all-middlesex-county-posts/cromwell-scoop-wingstop-coming-to-cromwell</t>
         </is>
